--- a/ROOT学习计划表.xlsx
+++ b/ROOT学习计划表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yemingxin/ROOT_Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FF7CCF-0CAC-1F46-882A-A484C4CA142E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C2E089-2189-9C44-B07A-EB4D4B3052C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
+    <workbookView xWindow="3760" yWindow="7040" windowWidth="37560" windowHeight="16600" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -83,6 +83,22 @@
   </si>
   <si>
     <t>抄写&amp;&amp;微调</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tchain读取两个root文件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>write_from_memory/Tchain/TestKinematics.C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>默写</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不使用Tfile::Open 而是使用Tchain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -487,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87CE0FF-AAD0-3E4F-9546-3652FADED723}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.83203125" defaultRowHeight="28" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="20.83203125" style="1"/>
@@ -545,6 +561,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="3" spans="1:7" ht="28" customHeight="1">
+      <c r="A3" s="1">
+        <v>20260626</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ROOT学习计划表.xlsx
+++ b/ROOT学习计划表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yemingxin/ROOT_Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C2E089-2189-9C44-B07A-EB4D4B3052C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA71295-465A-6E4A-8144-26B40F559A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="7040" windowWidth="37560" windowHeight="16600" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
+    <workbookView xWindow="2040" yWindow="5400" windowWidth="42200" windowHeight="17700" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -99,6 +99,29 @@
   </si>
   <si>
     <t>不使用Tfile::Open 而是使用Tchain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TChain读取两个root文件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用结构体+动态数组处理多重击中hit</t>
+  </si>
+  <si>
+    <t>使用结构体+动态数组处理多重击中hit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>write_from_memory/动态数组/ReadFDCData2.C .h</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI生成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不在使用std::vector&lt;std::tuple&lt;int, int, int, int, double&gt;&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -503,15 +526,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87CE0FF-AAD0-3E4F-9546-3652FADED723}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.83203125" defaultRowHeight="28" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="20.83203125" style="1"/>
-    <col min="3" max="3" width="60.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="83.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="40.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="80.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="80.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="100.83203125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="20.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -569,7 +592,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -582,6 +605,29 @@
       </c>
       <c r="G3" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28" customHeight="1">
+      <c r="A4" s="1">
+        <v>20260720</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/ROOT学习计划表.xlsx
+++ b/ROOT学习计划表.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yemingxin/ROOT_Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA71295-465A-6E4A-8144-26B40F559A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3121809-414E-F048-AD72-4CE71595115A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="5400" windowWidth="42200" windowHeight="17700" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16760" xr2:uid="{815F353C-5B02-6E46-A63C-E294EBF5E0AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -122,6 +121,26 @@
   </si>
   <si>
     <t>不在使用std::vector&lt;std::tuple&lt;int, int, int, int, double&gt;&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lzh数据分析ROOT tips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在虚拟机练习lzh数据分析ROOTTips的Example</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义TF1函数，用h-&gt;FillRandom()生成TF1的随机数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把DeltaE-E曲线拉直成Ef-E然后做Ef的柱状图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>write_from_memory/粒子鉴别/PID.C</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87CE0FF-AAD0-3E4F-9546-3652FADED723}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.83203125" defaultRowHeight="28" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="20.83203125" style="1"/>
@@ -630,6 +649,45 @@
         <v>21</v>
       </c>
     </row>
+    <row r="5" spans="1:7" ht="28" customHeight="1">
+      <c r="A5" s="1">
+        <v>20260721</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28" customHeight="1">
+      <c r="A6" s="1">
+        <v>20260722</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28" customHeight="1">
+      <c r="A7" s="1">
+        <v>20260722</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
